--- a/data/trans_bre/P19C09-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P19C09-Estudios-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,1</t>
+          <t>-0,7; 3,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 2,45</t>
+          <t>-0,5; 2,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 2,57</t>
+          <t>-1,46; 2,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,44; 114,86</t>
+          <t>-15,22; 113,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 236,1</t>
+          <t>-21,3; 215,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-42,41; 130,75</t>
+          <t>-37,23; 120,31</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 0,51</t>
+          <t>-1,92; 0,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,43</t>
+          <t>0,29; 2,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 0,12</t>
+          <t>-1,98; 0,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-59,48; 36,13</t>
+          <t>-59,02; 33,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,2; 272,48</t>
+          <t>10,63; 264,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-57,87; 5,69</t>
+          <t>-58,39; 6,14</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 4,58</t>
+          <t>-0,05; 4,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 2,62</t>
+          <t>-2,33; 2,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 4,12</t>
+          <t>-0,84; 4,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,02; 557,76</t>
+          <t>-23,43; 527,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-59,9; 134,43</t>
+          <t>-52,96; 141,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,94; 260,77</t>
+          <t>-28,5; 242,18</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,46</t>
+          <t>-0,34; 1,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,98</t>
+          <t>0,3; 1,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,7</t>
+          <t>-1,08; 0,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 68,66</t>
+          <t>-11,74; 69,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,46; 150,68</t>
+          <t>10,33; 129,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,93; 31,31</t>
+          <t>-31,93; 31,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C09-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P19C09-Estudios-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 3,14</t>
+          <t>-0,65; 3,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 2,54</t>
+          <t>-0,45; 2,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 2,43</t>
+          <t>-1,67; 2,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 113,54</t>
+          <t>-13,96; 129,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,3; 215,74</t>
+          <t>-22,35; 216,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-37,23; 120,31</t>
+          <t>-41,0; 133,3</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,5</t>
+          <t>-1,91; 0,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,44</t>
+          <t>0,35; 2,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,07</t>
+          <t>-2,11; 0,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-59,02; 33,51</t>
+          <t>-60,1; 27,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,63; 264,15</t>
+          <t>18,48; 278,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-58,39; 6,14</t>
+          <t>-58,57; 6,5</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 4,57</t>
+          <t>0,16; 4,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 2,54</t>
+          <t>-2,45; 2,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 4,09</t>
+          <t>-0,52; 4,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-23,43; 527,4</t>
+          <t>-10,2; 602,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-52,96; 141,78</t>
+          <t>-55,29; 137,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-28,5; 242,18</t>
+          <t>-20,6; 282,7</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,45</t>
+          <t>-0,35; 1,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,9</t>
+          <t>0,33; 1,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,76</t>
+          <t>-1,09; 0,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 69,72</t>
+          <t>-11,64; 66,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,33; 129,59</t>
+          <t>13,93; 137,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,93; 31,13</t>
+          <t>-31,62; 30,5</t>
         </is>
       </c>
     </row>
